--- a/artfynd/A 27325-2026 artfynd.xlsx
+++ b/artfynd/A 27325-2026 artfynd.xlsx
@@ -14978,7 +14978,7 @@
         <v>136133351</v>
       </c>
       <c r="B139" t="n">
-        <v>106483</v>
+        <v>106486</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 27325-2026 artfynd.xlsx
+++ b/artfynd/A 27325-2026 artfynd.xlsx
@@ -14978,7 +14978,7 @@
         <v>136133351</v>
       </c>
       <c r="B139" t="n">
-        <v>106486</v>
+        <v>106487</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 27325-2026 artfynd.xlsx
+++ b/artfynd/A 27325-2026 artfynd.xlsx
@@ -9043,7 +9043,7 @@
         <v>136573214</v>
       </c>
       <c r="B83" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>136573212</v>
       </c>
       <c r="B106" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>136573224</v>
       </c>
       <c r="B107" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>136133351</v>
       </c>
       <c r="B139" t="n">
-        <v>106487</v>
+        <v>106492</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 27325-2026 artfynd.xlsx
+++ b/artfynd/A 27325-2026 artfynd.xlsx
@@ -9043,7 +9043,7 @@
         <v>136573214</v>
       </c>
       <c r="B83" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 27325-2026 artfynd.xlsx
+++ b/artfynd/A 27325-2026 artfynd.xlsx
@@ -9043,7 +9043,7 @@
         <v>136573214</v>
       </c>
       <c r="B83" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 27325-2026 artfynd.xlsx
+++ b/artfynd/A 27325-2026 artfynd.xlsx
@@ -9043,7 +9043,7 @@
         <v>136573214</v>
       </c>
       <c r="B83" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 27325-2026 artfynd.xlsx
+++ b/artfynd/A 27325-2026 artfynd.xlsx
@@ -9043,7 +9043,7 @@
         <v>136573214</v>
       </c>
       <c r="B83" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 27325-2026 artfynd.xlsx
+++ b/artfynd/A 27325-2026 artfynd.xlsx
@@ -9043,7 +9043,7 @@
         <v>136573214</v>
       </c>
       <c r="B83" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
